--- a/data/gravel/Sklar SS Ti 2025.xlsx
+++ b/data/gravel/Sklar SS Ti 2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6E89DB-E7AA-D843-956D-886CDEB70343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDF9AE3-B72D-764E-8E3A-A9EBFFC0ACBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="26340" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -339,6 +339,24 @@
   </si>
   <si>
     <t>trail</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -677,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1262,197 +1280,197 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>60</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>94</v>
+        <v>104</v>
+      </c>
+      <c r="B38" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>106</v>
+      </c>
+      <c r="B39" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>60</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>62</v>
       </c>
-      <c r="B40">
+      <c r="B43">
         <f>2.2*25.4</f>
         <v>55.88</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>65</v>
-      </c>
-    </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>70</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>72</v>
-      </c>
-      <c r="B50">
-        <v>27.2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="B53">
+        <v>27.2</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>76</v>
+        <v>73</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>79</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>82</v>
+        <v>79</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>83</v>
-      </c>
-      <c r="B61">
-        <v>2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>84</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>85</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>86</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>94</v>
+        <v>83</v>
+      </c>
+      <c r="B64">
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>87</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>94</v>
@@ -1460,24 +1478,48 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>90</v>
-      </c>
-      <c r="B68">
-        <v>2599</v>
+        <v>87</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>91</v>
+        <v>88</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>92</v>
+        <v>89</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>90</v>
+      </c>
+      <c r="B71">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>93</v>
       </c>
     </row>

--- a/data/gravel/Sklar SS Ti 2025.xlsx
+++ b/data/gravel/Sklar SS Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDF9AE3-B72D-764E-8E3A-A9EBFFC0ACBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6F76AD-09E1-0848-BDBA-A47E4DF97076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="26340" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,9 +44,6 @@
     <t>model</t>
   </si>
   <si>
-    <t xml:space="preserve">SS Ti </t>
-  </si>
-  <si>
     <t>model_year</t>
   </si>
   <si>
@@ -357,6 +354,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supersomething Ti </t>
   </si>
 </sst>
 </file>
@@ -713,71 +713,71 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="B2" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>13</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>14</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
         <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
       </c>
       <c r="C9">
         <v>543</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
         <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
       </c>
       <c r="C10">
         <v>347</v>
@@ -820,10 +820,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
         <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
       </c>
       <c r="C11">
         <v>507</v>
@@ -843,10 +843,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
         <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
       </c>
       <c r="C12">
         <v>585</v>
@@ -866,10 +866,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
         <v>25</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
       </c>
       <c r="C13">
         <v>287</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
         <v>27</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
       </c>
       <c r="C14">
         <v>69.5</v>
@@ -912,10 +912,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
         <v>29</v>
-      </c>
-      <c r="B15" t="s">
-        <v>30</v>
       </c>
       <c r="C15">
         <v>73.5</v>
@@ -935,10 +935,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
         <v>31</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
       </c>
       <c r="C16">
         <v>426</v>
@@ -958,10 +958,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
         <v>33</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
       </c>
       <c r="C17">
         <v>73</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
         <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
       </c>
       <c r="C18">
         <v>412</v>
@@ -1004,10 +1004,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19">
         <v>76</v>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
         <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
       </c>
       <c r="C20">
         <v>55</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
         <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
         <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
       </c>
       <c r="C22">
         <v>440</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
         <v>44</v>
-      </c>
-      <c r="B23" t="s">
-        <v>45</v>
       </c>
       <c r="C23">
         <v>735</v>
@@ -1119,43 +1119,43 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C30">
         <v>700</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C31">
         <v>45</v>
@@ -1198,10 +1198,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C32">
         <f>2.2*25.4</f>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C33">
         <v>160.02000000000001</v>
@@ -1249,10 +1249,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C34">
         <v>169.68</v>
@@ -1272,60 +1272,60 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" t="s">
         <v>56</v>
-      </c>
-      <c r="B36" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" t="s">
         <v>102</v>
-      </c>
-      <c r="B37" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" t="s">
         <v>104</v>
-      </c>
-      <c r="B38" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" t="s">
         <v>106</v>
-      </c>
-      <c r="B39" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" t="s">
         <v>58</v>
-      </c>
-      <c r="B40" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43">
         <f>2.2*25.4</f>
@@ -1334,55 +1334,55 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B53">
         <v>27.2</v>
@@ -1390,63 +1390,63 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -1454,7 +1454,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -1462,47 +1462,47 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B71">
         <v>2599</v>
@@ -1510,17 +1510,17 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
